--- a/EVAP4 Angled Deposition.xlsx
+++ b/EVAP4 Angled Deposition.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mickd\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9D04485-ADF4-4B5D-A8A3-61C9F7825CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DB1C4B2-9FFA-40BE-A7FA-F46DF4B0E904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" activeTab="2" xr2:uid="{D6AA45CB-83A4-4966-9D86-A35E599A57DD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" firstSheet="2" activeTab="3" xr2:uid="{D6AA45CB-83A4-4966-9D86-A35E599A57DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Process Flow" sheetId="3" r:id="rId1"/>
     <sheet name="Run Sheet" sheetId="5" r:id="rId2"/>
     <sheet name="Wafer Status" sheetId="6" r:id="rId3"/>
+    <sheet name="Pad widths" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="99">
   <si>
     <t>Step</t>
   </si>
@@ -169,6 +170,12 @@
     <t>Determine post-deposition trench widths</t>
   </si>
   <si>
+    <t>13 DEKTAK</t>
+  </si>
+  <si>
+    <t>Measure deposition thickness</t>
+  </si>
+  <si>
     <t>Run</t>
   </si>
   <si>
@@ -190,19 +197,31 @@
     <t>Cu</t>
   </si>
   <si>
+    <t>test run</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>didn't tilt, ran with actual angle of 0 :(</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>loaded 180° backwards</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
     <t>A2</t>
   </si>
   <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>A6</t>
+    <t>forgot kapton tape, could measure pins</t>
   </si>
   <si>
     <t>A7</t>
@@ -280,44 +299,50 @@
     <t>Diagonal</t>
   </si>
   <si>
-    <t>didn't tilt, ran with actual angle of 0 :(</t>
-  </si>
-  <si>
-    <t>backup</t>
-  </si>
-  <si>
-    <t>13 DEKTAK</t>
-  </si>
-  <si>
-    <t>Measure deposition thickness</t>
+    <t>Deposition Rate (A/s)</t>
+  </si>
+  <si>
+    <t>Dektak:</t>
+  </si>
+  <si>
+    <t>no kapton</t>
   </si>
   <si>
     <t>45 failed</t>
   </si>
   <si>
-    <t>Deposition Rate (A/s)</t>
-  </si>
-  <si>
-    <t>loaded 180° backwards</t>
-  </si>
-  <si>
-    <t>forgot kapton tape, could measure pins</t>
-  </si>
-  <si>
-    <t>test run</t>
-  </si>
-  <si>
-    <t>no kapton</t>
-  </si>
-  <si>
     <t>180° rotation</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>one-way kapton</t>
+  </si>
+  <si>
+    <t>Post-evap pad width (North)</t>
+  </si>
+  <si>
+    <t>Post-evap pad width (East)</t>
+  </si>
+  <si>
+    <t>Post-evap pad width (South)</t>
+  </si>
+  <si>
+    <t>Post-evap pad width (West)</t>
+  </si>
+  <si>
+    <t>Post-evap pad width (Center)</t>
+  </si>
+  <si>
+    <t>Post-evap pad width (Average)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,8 +429,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <i/>
       <sz val="10"/>
-      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -418,8 +449,8 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="9">
@@ -581,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -647,9 +678,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -670,30 +698,71 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -705,32 +774,8 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -747,6 +792,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1067,7 +1116,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA101DAB-7321-4417-BD17-59DEA17BC6FB}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" customWidth="1"/>
@@ -1077,7 +1126,7 @@
     <col min="6" max="6" width="55.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1094,16 +1143,16 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-    </row>
-    <row r="3" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+    </row>
+    <row r="3" spans="1:6" ht="66">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1120,7 +1169,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="66">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1138,24 +1187,24 @@
       </c>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="27">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="34" t="s">
         <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="53.4">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -1166,14 +1215,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="27">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3"/>
@@ -1181,7 +1230,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="66.599999999999994" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="66.599999999999994">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -1196,7 +1245,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="66.599999999999994" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="66.599999999999994">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1213,7 +1262,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="40.200000000000003">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
@@ -1229,7 +1278,7 @@
       </c>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="26.4">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -1246,7 +1295,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="40.200000000000003">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
@@ -1259,25 +1308,25 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="26.4">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -1293,44 +1342,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1C2B0B0-0ECE-4CBF-824B-46CE2AFD96BB}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="10.109375" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" customWidth="1"/>
     <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="29.88671875" customWidth="1"/>
+    <col min="6" max="6" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>48</v>
+      <c r="B2" s="27" t="s">
+        <v>50</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" s="14">
         <v>500</v>
@@ -1339,18 +1388,18 @@
         <v>0</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="D3" s="14">
         <v>500</v>
@@ -1359,18 +1408,18 @@
         <v>45</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="28" t="s">
-        <v>52</v>
+      <c r="B4" s="27" t="s">
+        <v>55</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D4" s="14">
         <v>500</v>
@@ -1380,15 +1429,15 @@
       </c>
       <c r="F4" s="18"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>53</v>
+      <c r="B5" s="30" t="s">
+        <v>56</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" s="14">
         <v>500</v>
@@ -1397,18 +1446,18 @@
         <v>30</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>54</v>
+      <c r="B6" s="30" t="s">
+        <v>58</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" s="14">
         <v>500</v>
@@ -1418,15 +1467,15 @@
       </c>
       <c r="F6" s="18"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>50</v>
+      <c r="B7" s="30" t="s">
+        <v>59</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7" s="14">
         <v>500</v>
@@ -1435,32 +1484,36 @@
         <v>20</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>55</v>
+      <c r="B8" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="13"/>
+        <v>51</v>
+      </c>
+      <c r="D8" s="14">
+        <v>500</v>
+      </c>
+      <c r="E8" s="13">
+        <v>25</v>
+      </c>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="32" t="s">
-        <v>56</v>
+      <c r="B9" s="31" t="s">
+        <v>62</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
@@ -1473,8 +1526,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE59E293-AC48-4D4B-BECA-3A9294B901D0}">
-  <dimension ref="A1:AW26"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BO26"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="8.5546875" style="9"/>
@@ -1521,237 +1574,270 @@
     <col min="51" max="51" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="L1" s="54"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="O1" s="54"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="R1" s="54"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="U1" s="54"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="47" t="s">
+    <row r="1" spans="1:67" ht="14.85" customHeight="1">
+      <c r="C1" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="44" t="s">
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="48"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" s="48"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="R1" s="48"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="U1" s="48"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="45"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI1" s="42"/>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL1" s="42"/>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="AO1" s="42"/>
-      <c r="AP1" s="43"/>
-      <c r="AQ1" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="AR1" s="42"/>
-      <c r="AS1" s="43"/>
-      <c r="AT1" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="AU1" s="39"/>
-      <c r="AV1" s="40"/>
+      <c r="AA1" s="57"/>
+      <c r="AB1" s="57"/>
+      <c r="AC1" s="57"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI1" s="54"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL1" s="54"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO1" s="54"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR1" s="54"/>
+      <c r="AS1" s="55"/>
+      <c r="AT1" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="52"/>
       <c r="AW1" s="24" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:49" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="AX1" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="AY1" s="39"/>
+      <c r="AZ1" s="40"/>
+      <c r="BA1" s="38" t="s">
         <v>71</v>
       </c>
+      <c r="BB1" s="39"/>
+      <c r="BC1" s="40"/>
+      <c r="BD1" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="BE1" s="39"/>
+      <c r="BF1" s="40"/>
+      <c r="BG1" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="BH1" s="39"/>
+      <c r="BI1" s="40"/>
+      <c r="BJ1" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK1" s="39"/>
+      <c r="BL1" s="40"/>
+      <c r="BM1" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="BN1" s="36"/>
+      <c r="BO1" s="37"/>
+    </row>
+    <row r="2" spans="1:67" ht="30" customHeight="1">
+      <c r="A2" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>77</v>
+      </c>
       <c r="C2" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="36" t="s">
-        <v>77</v>
+        <v>82</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="N2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="P2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="Q2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="S2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="T2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="T2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="U2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="V2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="W2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="W2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="Y2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z2" s="36" t="s">
-        <v>45</v>
+        <v>85</v>
+      </c>
+      <c r="Z2" s="33" t="s">
+        <v>47</v>
       </c>
       <c r="AA2" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AC2" s="23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="AE2" s="36" t="s">
-        <v>77</v>
+      <c r="AE2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="AF2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AG2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="AH2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="AI2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AJ2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="AK2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="AL2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AM2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="AN2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="AO2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AP2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="AQ2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="AR2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AS2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT2" s="36" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="AT2" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="AU2" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AV2" s="23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="30" t="s">
-        <v>48</v>
+        <v>85</v>
+      </c>
+      <c r="AX2" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:67" ht="14.4">
+      <c r="A3" s="29" t="s">
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C3">
         <v>6.0039999999999996</v>
@@ -1809,7 +1895,7 @@
         <v>6.3775000000000004</v>
       </c>
       <c r="Z3" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA3">
         <v>500</v>
@@ -1820,8 +1906,11 @@
       <c r="AC3">
         <v>7</v>
       </c>
+      <c r="AD3" s="9" t="s">
+        <v>92</v>
+      </c>
       <c r="AE3" s="12">
-        <f t="shared" ref="AE3:AS3" si="1">AVERAGE(0, 0, 0, 0)</f>
+        <f t="shared" ref="AE3:AT3" si="1">AVERAGE(0, 0, 0, 0)</f>
         <v>0</v>
       </c>
       <c r="AF3" s="12">
@@ -1881,25 +1970,43 @@
         <v>0</v>
       </c>
       <c r="AT3" s="12">
-        <f t="shared" ref="AT3:AV10" si="2">AVERAGE(AE3,AH3,AK3,AN3,AQ3)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AU3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AT3:AV10" si="2">AVERAGE(AF3,AI3,AL3,AO3,AR3)</f>
         <v>0</v>
       </c>
       <c r="AV3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AW3" s="25"/>
-    </row>
-    <row r="4" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
-        <v>50</v>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f>AVERAGE(556.6,554.7,539.4,545.9)</f>
+        <v>549.15000000000009</v>
+      </c>
+      <c r="BG3">
+        <f>AVERAGE(553.6,561.4,547.5,528.2)</f>
+        <v>547.67499999999995</v>
+      </c>
+      <c r="BJ3">
+        <f>AVERAGE(552.9,558.4,569.1,576)</f>
+        <v>564.1</v>
+      </c>
+      <c r="BM3">
+        <f>AVERAGE(BA3,BG3,BJ3)</f>
+        <v>553.64166666666677</v>
+      </c>
+    </row>
+    <row r="4" spans="1:67" ht="14.4">
+      <c r="A4" s="29" t="s">
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="C4">
         <v>6.0460000000000003</v>
@@ -1989,7 +2096,7 @@
         <v>6.5870000000000006</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA4">
         <v>500</v>
@@ -2000,9 +2107,11 @@
       <c r="AC4">
         <v>10</v>
       </c>
+      <c r="AD4" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="AE4" s="9">
-        <f>AVERAGE(6.8, 6.83, 7.47, 6.92)</f>
-        <v>7.004999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="12">
         <f>AVERAGE(1.61, 1.7, 1.48, 1.74)</f>
@@ -2013,8 +2122,7 @@
         <v>1.6375000000000002</v>
       </c>
       <c r="AH4" s="9">
-        <f>AVERAGE(6.56, 6.41, 6.09, 6.51)</f>
-        <v>6.3925000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="12">
         <f>AVERAGE(1.67, 1.77, 1.66, 1.76)</f>
@@ -2025,8 +2133,7 @@
         <v>1.73</v>
       </c>
       <c r="AK4" s="9">
-        <f>AVERAGE(6.75, 6.82, 6.6, 6.75)</f>
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="12">
         <f>AVERAGE(1.39, 1.24, 1.21, 1.25)</f>
@@ -2037,8 +2144,7 @@
         <v>1.73</v>
       </c>
       <c r="AN4" s="9">
-        <f>AVERAGE(6.96, 6.74, 6.81, 6.51)</f>
-        <v>6.754999999999999</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="12">
         <f>AVERAGE(1.69, 1.79, 1.94, 1.62)</f>
@@ -2049,8 +2155,7 @@
         <v>1.825</v>
       </c>
       <c r="AQ4" s="9">
-        <f>AVERAGE(6.76, 6.49, 6.54, 6.38)</f>
-        <v>6.5424999999999995</v>
+        <v>0</v>
       </c>
       <c r="AR4" s="12">
         <f>AVERAGE(1.38, 1.52, 1.56, 1.46)</f>
@@ -2060,9 +2165,8 @@
         <f>AVERAGE(1.45, 1.46, 1.62, 1.59)</f>
         <v>1.53</v>
       </c>
-      <c r="AT4" s="12">
-        <f t="shared" si="2"/>
-        <v>6.6849999999999996</v>
+      <c r="AT4" s="9">
+        <v>0</v>
       </c>
       <c r="AU4">
         <f t="shared" si="2"/>
@@ -2072,14 +2176,28 @@
         <f t="shared" si="2"/>
         <v>1.6905000000000001</v>
       </c>
-      <c r="AW4" s="25"/>
-    </row>
-    <row r="5" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
-        <v>51</v>
+      <c r="AW4">
+        <v>20</v>
+      </c>
+      <c r="AX4">
+        <f>AVERAGE(419.3,424.3,405.8,428)</f>
+        <v>419.35</v>
+      </c>
+      <c r="BD4">
+        <f>AVERAGE(507.3,490,454.5,465.9)</f>
+        <v>479.42499999999995</v>
+      </c>
+      <c r="BM4">
+        <f>AVERAGE(AX4,BD4)</f>
+        <v>449.38749999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:67" ht="14.4">
+      <c r="A5" s="29" t="s">
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="C5">
         <v>6.0140000000000002</v>
@@ -2169,7 +2287,7 @@
         <v>6.520999999999999</v>
       </c>
       <c r="Z5" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA5">
         <v>500</v>
@@ -2181,10 +2299,10 @@
         <v>10</v>
       </c>
       <c r="AD5" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AE5" s="12">
-        <f t="shared" ref="AE5:AS5" si="3">AVERAGE(0, 0, 0, 0)</f>
+        <f t="shared" ref="AE5:AT5" si="3">AVERAGE(0, 0, 0, 0)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="12">
@@ -2244,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="AT5" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AU5">
@@ -2255,13 +2373,40 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
-        <v>52</v>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f>AVERAGE(576.4,583.5,569.9,569.7)</f>
+        <v>574.875</v>
+      </c>
+      <c r="BA5">
+        <f>AVERAGE(531.1,534.2,531.9,551.9)</f>
+        <v>537.27500000000009</v>
+      </c>
+      <c r="BD5">
+        <f>AVERAGE(554.2,535.7,539.4,512.7)</f>
+        <v>535.5</v>
+      </c>
+      <c r="BG5">
+        <f>AVERAGE(540.8,534.9,546.6,564.6)</f>
+        <v>546.72499999999991</v>
+      </c>
+      <c r="BJ5">
+        <f>AVERAGE(529.2,552,557.7,554.7)</f>
+        <v>548.40000000000009</v>
+      </c>
+      <c r="BM5">
+        <f>AVERAGE(AX5,BA5,BD5,BG5,BJ5)</f>
+        <v>548.55500000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:67" ht="14.4">
+      <c r="A6" s="26" t="s">
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C6">
         <v>6.0279999999999996</v>
@@ -2339,7 +2484,7 @@
         <v>6.5949999999999998</v>
       </c>
       <c r="W6" s="12">
-        <f t="shared" ref="W6:Y8" si="4">AVERAGE(H6,K6,N6,Q6,T6)</f>
+        <f t="shared" ref="W6:Y10" si="4">AVERAGE(H6,K6,N6,Q6,T6)</f>
         <v>6.6975000000000007</v>
       </c>
       <c r="X6">
@@ -2351,7 +2496,7 @@
         <v>6.6044999999999998</v>
       </c>
       <c r="Z6" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA6">
         <v>500</v>
@@ -2366,8 +2511,7 @@
         <v>90</v>
       </c>
       <c r="AE6" s="9">
-        <f>AVERAGE(6.54, 6.62, 6.32, 6.56)</f>
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="12">
         <f>AVERAGE(4.99, 5.1, 4.64, 4.64)</f>
@@ -2378,8 +2522,7 @@
         <v>4.7250000000000005</v>
       </c>
       <c r="AH6" s="9">
-        <f>AVERAGE(6.79, 6.54, 6.76, 6.41)</f>
-        <v>6.625</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="12">
         <f>AVERAGE(4.26, 4.26, 4.34, 4.55)</f>
@@ -2390,8 +2533,7 @@
         <v>4.4749999999999996</v>
       </c>
       <c r="AK6" s="9">
-        <f>AVERAGE(6.66, 6.82, 6.85, 6.53)</f>
-        <v>6.7149999999999999</v>
+        <v>0</v>
       </c>
       <c r="AL6" s="12">
         <f>AVERAGE(4.82, 4.68, 4.96, 5.1)</f>
@@ -2402,8 +2544,7 @@
         <v>4.21</v>
       </c>
       <c r="AN6" s="9">
-        <f>AVERAGE(6.78, 6.88, 6.79, 6.92)</f>
-        <v>6.8424999999999994</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="12">
         <f>AVERAGE(4.71, 4.71, 4.4, 4.98)</f>
@@ -2414,8 +2555,7 @@
         <v>4.72</v>
       </c>
       <c r="AQ6" s="9">
-        <f>AVERAGE(6.68, 6.77, 6.9, 6.83)</f>
-        <v>6.7949999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR6" s="12">
         <f>AVERAGE(5.27, 5.11, 5.52, 5.46)</f>
@@ -2425,9 +2565,8 @@
         <f>AVERAGE(5.27, 5.24, 5.64, 5.62)</f>
         <v>5.4424999999999999</v>
       </c>
-      <c r="AT6" s="12">
-        <f t="shared" si="2"/>
-        <v>6.6975000000000007</v>
+      <c r="AT6" s="9">
+        <v>0</v>
       </c>
       <c r="AU6">
         <f t="shared" si="2"/>
@@ -2437,13 +2576,40 @@
         <f t="shared" si="2"/>
         <v>4.7144999999999992</v>
       </c>
-    </row>
-    <row r="7" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
-        <v>53</v>
+      <c r="AW6">
+        <v>45</v>
+      </c>
+      <c r="AX6">
+        <f>AVERAGE(322,295,312,321)</f>
+        <v>312.5</v>
+      </c>
+      <c r="BA6">
+        <f>AVERAGE(336,358,375,380)</f>
+        <v>362.25</v>
+      </c>
+      <c r="BD6">
+        <f>AVERAGE(445,450,404,414)</f>
+        <v>428.25</v>
+      </c>
+      <c r="BG6">
+        <f>AVERAGE(330,326,384,409)</f>
+        <v>362.25</v>
+      </c>
+      <c r="BJ6">
+        <f>AVERAGE(422,438,449,443)</f>
+        <v>438</v>
+      </c>
+      <c r="BM6">
+        <f>AVERAGE(AX6,BA6,BD6,BG6,BJ6)</f>
+        <v>380.65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:67" ht="14.4">
+      <c r="A7" s="26" t="s">
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C7">
         <v>6.02</v>
@@ -2533,7 +2699,7 @@
         <v>6.4535000000000009</v>
       </c>
       <c r="Z7" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA7">
         <v>500</v>
@@ -2545,8 +2711,7 @@
         <v>10</v>
       </c>
       <c r="AE7" s="9">
-        <f>AVERAGE(6.39, 6.56, 6.2, 6.39)</f>
-        <v>6.3849999999999998</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="12">
         <f>AVERAGE(1.57, 1.77, 1.85, 1.65)</f>
@@ -2557,8 +2722,7 @@
         <v>1.2825</v>
       </c>
       <c r="AH7" s="9">
-        <f>AVERAGE(6.56, 6.24, 6.76, 6.25)</f>
-        <v>6.4525000000000006</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="12">
         <f>AVERAGE(2.12, 2.21, 2.53, 2.86)</f>
@@ -2569,8 +2733,7 @@
         <v>2.4125000000000001</v>
       </c>
       <c r="AK7" s="9">
-        <f>AVERAGE(6.67, 6.6, 6.3, 6.82)</f>
-        <v>6.5975000000000001</v>
+        <v>0</v>
       </c>
       <c r="AL7" s="12">
         <f>AVERAGE(2.22, 2.54, 2.55, 2.72)</f>
@@ -2581,8 +2744,7 @@
         <v>1.8325</v>
       </c>
       <c r="AN7" s="9">
-        <f>AVERAGE(6.48, 6.58, 6.46, 6.45)</f>
-        <v>6.4924999999999997</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="12">
         <f>AVERAGE(1.99, 2.16, 2.16, 2.17)</f>
@@ -2593,8 +2755,7 @@
         <v>1.7849999999999997</v>
       </c>
       <c r="AQ7" s="9">
-        <f>AVERAGE(6.78, 6.59, 6.48, 6.37)</f>
-        <v>6.5550000000000006</v>
+        <v>0</v>
       </c>
       <c r="AR7" s="12">
         <f>AVERAGE(2.09, 2.36, 2.25, 2.41)</f>
@@ -2604,9 +2765,8 @@
         <f>AVERAGE(1.98, 2.06, 2.13, 2.1)</f>
         <v>2.0674999999999999</v>
       </c>
-      <c r="AT7" s="12">
-        <f t="shared" si="2"/>
-        <v>6.4965000000000002</v>
+      <c r="AT7" s="9">
+        <v>0</v>
       </c>
       <c r="AU7">
         <f t="shared" si="2"/>
@@ -2616,13 +2776,40 @@
         <f t="shared" si="2"/>
         <v>1.8759999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
-        <v>54</v>
+      <c r="AW7">
+        <v>30</v>
+      </c>
+      <c r="AX7">
+        <f>AVERAGE(445,513,504,501)</f>
+        <v>490.75</v>
+      </c>
+      <c r="BA7">
+        <f>AVERAGE(416,424,417,489)</f>
+        <v>436.5</v>
+      </c>
+      <c r="BD7">
+        <f>AVERAGE(410,402,403,401)</f>
+        <v>404</v>
+      </c>
+      <c r="BG7">
+        <f>AVERAGE(466,465,419,417)</f>
+        <v>441.75</v>
+      </c>
+      <c r="BJ7">
+        <f>AVERAGE(460,454,467,447)</f>
+        <v>457</v>
+      </c>
+      <c r="BM7">
+        <f>AVERAGE(AX7,BA7,BD7,BG7,BJ7)</f>
+        <v>446</v>
+      </c>
+    </row>
+    <row r="8" spans="1:67" ht="14.4">
+      <c r="A8" s="26" t="s">
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="C8">
         <v>6.0119999999999996</v>
@@ -2712,7 +2899,7 @@
         <v>6.51</v>
       </c>
       <c r="Z8" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA8">
         <v>500</v>
@@ -2723,12 +2910,8 @@
       <c r="AC8">
         <v>10</v>
       </c>
-      <c r="AD8" s="9" t="s">
-        <v>89</v>
-      </c>
       <c r="AE8" s="9">
-        <f>AVERAGE(6.77, 6.95, 6.39, 6.5)</f>
-        <v>6.6524999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="12">
         <f>AVERAGE(3.73, 3.65, 3.65, 3.39)</f>
@@ -2739,8 +2922,7 @@
         <v>3.02</v>
       </c>
       <c r="AH8" s="9">
-        <f>AVERAGE(6.26, 6.36, 6.46, 6.39)</f>
-        <v>6.3675000000000006</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="12">
         <f>AVERAGE(3.47, 3.47, 3.3, 3.47)</f>
@@ -2751,8 +2933,7 @@
         <v>3.3699999999999997</v>
       </c>
       <c r="AK8" s="9">
-        <f>AVERAGE(6.88, 6.28, 6.24, 6.24)</f>
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="AL8" s="12">
         <f>AVERAGE(3.56, 3.56, 3.39, 3.65)</f>
@@ -2763,8 +2944,7 @@
         <v>3.7774999999999999</v>
       </c>
       <c r="AN8" s="9">
-        <f>AVERAGE(6.75, 6.92, 6.73, 6.54)</f>
-        <v>6.7349999999999994</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="12">
         <f>AVERAGE(3.82, 3.39, 3.21, 3.47)</f>
@@ -2775,8 +2955,7 @@
         <v>3.2725</v>
       </c>
       <c r="AQ8" s="9">
-        <f>AVERAGE(6.54, 6.52, 6.79, 6.7)</f>
-        <v>6.6374999999999993</v>
+        <v>0</v>
       </c>
       <c r="AR8" s="12">
         <f>AVERAGE(3.39, 3.22, 3.47, 3.56)</f>
@@ -2786,9 +2965,8 @@
         <f>AVERAGE(3.42, 3.53, 3.18, 3.35)</f>
         <v>3.3699999999999997</v>
       </c>
-      <c r="AT8" s="12">
-        <f t="shared" si="2"/>
-        <v>6.5604999999999993</v>
+      <c r="AT8" s="9">
+        <v>0</v>
       </c>
       <c r="AU8">
         <f t="shared" si="2"/>
@@ -2798,13 +2976,40 @@
         <f t="shared" si="2"/>
         <v>3.3620000000000005</v>
       </c>
-    </row>
-    <row r="9" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
-        <v>55</v>
+      <c r="AW8">
+        <v>37.5</v>
+      </c>
+      <c r="AX8">
+        <f>AVERAGE(338,346,353,346)</f>
+        <v>345.75</v>
+      </c>
+      <c r="BA8">
+        <f>AVERAGE(446,427,375,358)</f>
+        <v>401.5</v>
+      </c>
+      <c r="BD8">
+        <f>AVERAGE(451.5,441.9,463.6,449.3)</f>
+        <v>451.57499999999999</v>
+      </c>
+      <c r="BG8">
+        <f>AVERAGE(333,405,343,334)</f>
+        <v>353.75</v>
+      </c>
+      <c r="BJ8">
+        <f>AVERAGE(402,439,447,489)</f>
+        <v>444.25</v>
+      </c>
+      <c r="BM8">
+        <f>AVERAGE(AX8,BA8,BD8,BG8,BJ8)</f>
+        <v>399.36500000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:67" ht="14.4">
+      <c r="A9" s="26" t="s">
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="C9">
         <v>6.0179999999999998</v>
@@ -2822,156 +3027,199 @@
         <v>0.6</v>
       </c>
       <c r="H9" s="9">
-        <f t="shared" ref="H9:V10" si="5">AVERAGE(0, 0, 0, 0)</f>
-        <v>0</v>
+        <f>AVERAGE(6.76, 6.51, 6.35, 6.43)</f>
+        <v>6.5124999999999993</v>
       </c>
       <c r="I9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.61, 6.64, 6.19, 6.71)</f>
+        <v>6.5375000000000005</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.69, 6.44, 6.97, 6.74)</f>
+        <v>6.7100000000000009</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.59, 6.51, 6.8, 6.73)</f>
+        <v>6.6574999999999998</v>
       </c>
       <c r="L9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.75, 6.63, 6.37, 6.38)</f>
+        <v>6.5324999999999998</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.37, 6.51, 6.73, 6.55)</f>
+        <v>6.54</v>
       </c>
       <c r="N9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.47, 6.18, 6.46, 6.87)</f>
+        <v>6.4950000000000001</v>
       </c>
       <c r="O9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.77, 6.33, 6.29, 6.9)</f>
+        <v>6.5724999999999998</v>
       </c>
       <c r="P9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.46, 6.58, 6.49, 6.26)</f>
+        <v>6.4474999999999998</v>
       </c>
       <c r="Q9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.74, 6.36, 6.67, 6.39)</f>
+        <v>6.5400000000000009</v>
       </c>
       <c r="R9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.5, 6.71, 6.14, 6.73)</f>
+        <v>6.5200000000000005</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.82, 6.89, 6.59, 6.75)</f>
+        <v>6.7625000000000002</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.39, 6.34, 6.3, 6.39)</f>
+        <v>6.3550000000000004</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.82, 6.35, 6.5, 6.59)</f>
+        <v>6.5650000000000004</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.38, 6.47, 6.48, 6.48)</f>
+        <v>6.4524999999999997</v>
       </c>
       <c r="W9" s="12">
-        <f t="shared" ref="W9:Y10" si="6">AVERAGE(H9,K9,N9,Q9,T9)</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>6.5120000000000005</v>
       </c>
       <c r="X9">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>6.5454999999999997</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AE9" s="12">
-        <f t="shared" ref="AE9:AS10" si="7">AVERAGE(0, 0, 0, 0)</f>
+        <f t="shared" si="4"/>
+        <v>6.5824999999999987</v>
+      </c>
+      <c r="Z9" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA9">
+        <v>500</v>
+      </c>
+      <c r="AB9">
+        <v>25</v>
+      </c>
+      <c r="AC9">
+        <v>10</v>
+      </c>
+      <c r="AE9" s="9">
         <v>0</v>
       </c>
       <c r="AF9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AVERAGE(2.09, 2.39, 2.3, 2.09)</f>
+        <v>2.2175000000000002</v>
       </c>
       <c r="AG9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AH9" s="12">
-        <f t="shared" si="7"/>
+        <f>AVERAGE(1.79, 1.75, 2.06, 2.53)</f>
+        <v>2.0324999999999998</v>
+      </c>
+      <c r="AH9" s="9">
         <v>0</v>
       </c>
       <c r="AI9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AVERAGE(1.7, 1.7, 1.87, 1.91)</f>
+        <v>1.7949999999999999</v>
       </c>
       <c r="AJ9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AK9" s="12">
-        <f t="shared" si="7"/>
+        <f>AVERAGE(2.12, 1.75, 1.98, 1.96)</f>
+        <v>1.9524999999999999</v>
+      </c>
+      <c r="AK9" s="9">
         <v>0</v>
       </c>
       <c r="AL9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AVERAGE(1.7, 1.83, 1.91, 1.7)</f>
+        <v>1.7850000000000001</v>
       </c>
       <c r="AM9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AN9" s="12">
-        <f t="shared" si="7"/>
+        <f>AVERAGE(1.31, 1.16, 1.26, 1.41)</f>
+        <v>1.2849999999999999</v>
+      </c>
+      <c r="AN9" s="9">
         <v>0</v>
       </c>
       <c r="AO9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AVERAGE(2.17, 2.09, 2.22, 2.22)</f>
+        <v>2.1750000000000003</v>
       </c>
       <c r="AP9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="12">
-        <f t="shared" si="7"/>
+        <f>AVERAGE(2.48, 2.34, 2.37, 2.22)</f>
+        <v>2.3525</v>
+      </c>
+      <c r="AQ9" s="9">
         <v>0</v>
       </c>
       <c r="AR9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AVERAGE(1.7, 1.91, 2, 1.91)</f>
+        <v>1.88</v>
       </c>
       <c r="AS9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AT9" s="12">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(1.92, 1.74, 1.97, 1.95)</f>
+        <v>1.895</v>
+      </c>
+      <c r="AT9" s="9">
         <v>0</v>
       </c>
       <c r="AU9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.9704999999999999</v>
       </c>
       <c r="AV9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
-        <v>56</v>
+        <v>1.9035</v>
+      </c>
+      <c r="AW9">
+        <v>25</v>
+      </c>
+      <c r="AX9" s="9">
+        <f>AVERAGE(416,391.6,403.1,427.5)</f>
+        <v>409.55</v>
+      </c>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="9">
+        <f>AVERAGE(444.8,447,433.4,420.8)</f>
+        <v>436.49999999999994</v>
+      </c>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="9">
+        <f>AVERAGE(416.9,443.6,444.2,473.8)</f>
+        <v>444.625</v>
+      </c>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="9">
+        <f>AVERAGE(463.4,446.9,420.1,449.4)</f>
+        <v>444.95000000000005</v>
+      </c>
+      <c r="BH9" s="12"/>
+      <c r="BI9" s="12"/>
+      <c r="BJ9" s="9">
+        <f>AVERAGE(357.5,378.4,430.6,437.5)</f>
+        <v>401</v>
+      </c>
+      <c r="BK9" s="12"/>
+      <c r="BL9" s="12"/>
+      <c r="BM9" s="12">
+        <f>AVERAGE(AX9,BA9,BD9,BG9,BJ9)</f>
+        <v>427.32499999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:67" ht="14.4">
+      <c r="A10" s="26" t="s">
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C10">
         <v>6.0259999999999998</v>
@@ -2989,178 +3237,173 @@
         <v>1.4</v>
       </c>
       <c r="H10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.37, 6.51, 6.83, 6.12)</f>
+        <v>6.4575000000000005</v>
       </c>
       <c r="I10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.6, 6.59, 6.26, 6.46)</f>
+        <v>6.4775</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.32, 6.71, 6.78, 6.8)</f>
+        <v>6.6525000000000007</v>
       </c>
       <c r="K10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.76, 6.55, 6.55, 6.83)</f>
+        <v>6.6724999999999994</v>
       </c>
       <c r="L10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.75, 6.68, 6.31, 6.79)</f>
+        <v>6.6324999999999994</v>
       </c>
       <c r="M10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.44, 6.33, 6.45, 6.41)</f>
+        <v>6.4074999999999998</v>
       </c>
       <c r="N10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.3, 6.29, 6.33, 6.7)</f>
+        <v>6.4050000000000002</v>
       </c>
       <c r="O10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.47, 6.34, 6.71, 6.79)</f>
+        <v>6.5774999999999997</v>
       </c>
       <c r="P10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.72, 6.7, 6.3, 6.22)</f>
+        <v>6.4849999999999994</v>
       </c>
       <c r="Q10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.85,6.98,6.44,6.24)</f>
+        <v>6.6274999999999995</v>
       </c>
       <c r="R10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.39,6.69,6.54,6.57)</f>
+        <v>6.5475000000000003</v>
       </c>
       <c r="S10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.65,6.65,6.4,6.38)</f>
+        <v>6.5200000000000005</v>
       </c>
       <c r="T10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.45, 6.7, 6.88, 6.46)</f>
+        <v>6.6225000000000005</v>
       </c>
       <c r="U10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.73, 6.58, 6.61, 6.78)</f>
+        <v>6.6750000000000007</v>
       </c>
       <c r="V10" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(6.77, 6.33, 6.43, 6.22)</f>
+        <v>6.4375</v>
       </c>
       <c r="W10" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>6.5570000000000004</v>
       </c>
       <c r="X10">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>6.581999999999999</v>
       </c>
       <c r="Y10" s="9">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AE10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AF10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AG10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AH10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AI10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AK10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AL10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AN10" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>6.5004999999999997</v>
+      </c>
+      <c r="AB10">
+        <v>55</v>
+      </c>
+      <c r="AE10" s="9">
+        <f>AF13</f>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="9">
+        <f>AI13</f>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="9">
+        <f>AL13</f>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="9">
+        <f>AO13</f>
         <v>0</v>
       </c>
       <c r="AO10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AVERAGE(1,0.75,0.71,0.96)</f>
+        <v>0.85499999999999998</v>
       </c>
       <c r="AP10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="12">
-        <f t="shared" si="7"/>
+        <f>AVERAGE(0.97,1.02,1.02,0.84)</f>
+        <v>0.96249999999999991</v>
+      </c>
+      <c r="AQ10" s="9">
+        <f>AR13</f>
         <v>0</v>
       </c>
       <c r="AR10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>AVERAGE(0.96,1.04,0.83,0.87)</f>
+        <v>0.92500000000000004</v>
       </c>
       <c r="AS10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AT10" s="12">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(1.08,1.09,0.99,0.95)</f>
+        <v>1.0275000000000001</v>
+      </c>
+      <c r="AT10" s="9">
+        <f>AU13</f>
         <v>0</v>
       </c>
       <c r="AU10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AV10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
-    </row>
-    <row r="12" spans="1:49" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
-    </row>
-    <row r="13" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
-    </row>
-    <row r="14" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
-    </row>
-    <row r="15" spans="1:49" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="27"/>
-    </row>
-    <row r="16" spans="1:49" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="14.4" x14ac:dyDescent="0.3"/>
+        <v>0.995</v>
+      </c>
+      <c r="AW10" s="10">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:67" ht="14.4">
+      <c r="A11" s="26"/>
+    </row>
+    <row r="12" spans="1:67" ht="18.75" customHeight="1">
+      <c r="A12" s="26"/>
+    </row>
+    <row r="13" spans="1:67" ht="14.4">
+      <c r="A13" s="26"/>
+    </row>
+    <row r="14" spans="1:67" ht="14.4">
+      <c r="A14" s="26"/>
+    </row>
+    <row r="15" spans="1:67" ht="14.4">
+      <c r="A15" s="26"/>
+    </row>
+    <row r="16" spans="1:67" ht="14.4"/>
+    <row r="17" ht="14.4"/>
+    <row r="18" ht="14.4"/>
+    <row r="19" ht="14.4"/>
+    <row r="20" ht="14.4"/>
+    <row r="21" ht="14.4"/>
+    <row r="22" ht="14.4"/>
+    <row r="23" ht="14.4"/>
+    <row r="24" ht="14.4"/>
+    <row r="25" ht="14.4"/>
+    <row r="26" ht="14.4"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="20">
+    <mergeCell ref="AT1:AV1"/>
+    <mergeCell ref="AK1:AM1"/>
+    <mergeCell ref="AN1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="W1:Y1"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="H1:J1"/>
@@ -3168,20 +3411,783 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:V1"/>
-    <mergeCell ref="AT1:AV1"/>
-    <mergeCell ref="AK1:AM1"/>
-    <mergeCell ref="AN1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
-    <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="BM1:BO1"/>
+    <mergeCell ref="AX1:AZ1"/>
+    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="BG1:BI1"/>
+    <mergeCell ref="BJ1:BL1"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E9FBBC-1AF9-4569-A636-023B1A320347}">
+  <dimension ref="A1:U18"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="21" width="11.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="D1" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="54"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" s="54"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="N1" s="54"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+    </row>
+    <row r="2" spans="1:21" ht="27">
+      <c r="A2" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="M2" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" s="23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="12">
+        <f>'Wafer Status'!H3-'Wafer Status'!AE3</f>
+        <v>6.43</v>
+      </c>
+      <c r="E3" s="12">
+        <f>'Wafer Status'!I3-'Wafer Status'!AF3</f>
+        <v>6.8225000000000007</v>
+      </c>
+      <c r="F3" s="12">
+        <f>'Wafer Status'!J3-'Wafer Status'!AG3</f>
+        <v>6.4250000000000007</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12">
+        <f>'Wafer Status'!L3-'Wafer Status'!AI3</f>
+        <v>6.3625000000000007</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12">
+        <f>'Wafer Status'!T3-'Wafer Status'!AQ3</f>
+        <v>6.6825000000000001</v>
+      </c>
+      <c r="Q3" s="12">
+        <f>'Wafer Status'!U3-'Wafer Status'!AR3</f>
+        <v>6.91</v>
+      </c>
+      <c r="R3" s="12">
+        <f>'Wafer Status'!V3-'Wafer Status'!AS3</f>
+        <v>6.33</v>
+      </c>
+      <c r="S3" s="12">
+        <f t="shared" ref="S3:U10" si="0">AVERAGE(D3,G3,J3,M3,P3)</f>
+        <v>6.5562500000000004</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="0"/>
+        <v>6.6983333333333341</v>
+      </c>
+      <c r="U3">
+        <f t="shared" si="0"/>
+        <v>6.3775000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="12">
+        <f>'Wafer Status'!H4-'Wafer Status'!AE4</f>
+        <v>7.004999999999999</v>
+      </c>
+      <c r="E4" s="12">
+        <f>'Wafer Status'!I4-'Wafer Status'!AF4</f>
+        <v>4.942499999999999</v>
+      </c>
+      <c r="F4" s="12">
+        <f>'Wafer Status'!J4-'Wafer Status'!AG4</f>
+        <v>5.09</v>
+      </c>
+      <c r="G4" s="12">
+        <f>'Wafer Status'!K4-'Wafer Status'!AH4</f>
+        <v>6.3925000000000001</v>
+      </c>
+      <c r="H4" s="12">
+        <f>'Wafer Status'!L4-'Wafer Status'!AI4</f>
+        <v>4.8550000000000004</v>
+      </c>
+      <c r="I4" s="12">
+        <f>'Wafer Status'!M4-'Wafer Status'!AJ4</f>
+        <v>4.9375</v>
+      </c>
+      <c r="J4" s="12">
+        <f>'Wafer Status'!N4-'Wafer Status'!AK4</f>
+        <v>6.73</v>
+      </c>
+      <c r="K4" s="12">
+        <f>'Wafer Status'!O4-'Wafer Status'!AL4</f>
+        <v>5.31</v>
+      </c>
+      <c r="L4" s="12">
+        <f>'Wafer Status'!P4-'Wafer Status'!AM4</f>
+        <v>4.7200000000000006</v>
+      </c>
+      <c r="M4" s="12">
+        <f>'Wafer Status'!Q4-'Wafer Status'!AN4</f>
+        <v>6.754999999999999</v>
+      </c>
+      <c r="N4" s="12">
+        <f>'Wafer Status'!R4-'Wafer Status'!AO4</f>
+        <v>4.6575000000000006</v>
+      </c>
+      <c r="O4" s="12">
+        <f>'Wafer Status'!S4-'Wafer Status'!AP4</f>
+        <v>4.835</v>
+      </c>
+      <c r="P4" s="12">
+        <f>'Wafer Status'!T4-'Wafer Status'!AQ4</f>
+        <v>6.5424999999999995</v>
+      </c>
+      <c r="Q4" s="12">
+        <f>'Wafer Status'!U4-'Wafer Status'!AR4</f>
+        <v>4.8825000000000003</v>
+      </c>
+      <c r="R4" s="12">
+        <f>'Wafer Status'!V4-'Wafer Status'!AS4</f>
+        <v>4.8999999999999995</v>
+      </c>
+      <c r="S4" s="12">
+        <f t="shared" si="0"/>
+        <v>6.6849999999999996</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="0"/>
+        <v>4.9295</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="0"/>
+        <v>4.8964999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="12">
+        <f>'Wafer Status'!H5-'Wafer Status'!AE5</f>
+        <v>6.7550000000000008</v>
+      </c>
+      <c r="E5" s="12">
+        <f>'Wafer Status'!I5-'Wafer Status'!AF5</f>
+        <v>6.6349999999999998</v>
+      </c>
+      <c r="F5" s="12">
+        <f>'Wafer Status'!J5-'Wafer Status'!AG5</f>
+        <v>6.77</v>
+      </c>
+      <c r="G5" s="12">
+        <f>'Wafer Status'!K5-'Wafer Status'!AH5</f>
+        <v>6.6274999999999995</v>
+      </c>
+      <c r="H5" s="12">
+        <f>'Wafer Status'!L5-'Wafer Status'!AI5</f>
+        <v>6.2875000000000005</v>
+      </c>
+      <c r="I5" s="12">
+        <f>'Wafer Status'!M5-'Wafer Status'!AJ5</f>
+        <v>6.3475000000000001</v>
+      </c>
+      <c r="J5" s="12">
+        <f>'Wafer Status'!N5-'Wafer Status'!AK5</f>
+        <v>6.57</v>
+      </c>
+      <c r="K5" s="12">
+        <f>'Wafer Status'!O5-'Wafer Status'!AL5</f>
+        <v>6.48</v>
+      </c>
+      <c r="L5" s="12">
+        <f>'Wafer Status'!P5-'Wafer Status'!AM5</f>
+        <v>6.3550000000000004</v>
+      </c>
+      <c r="M5" s="12">
+        <f>'Wafer Status'!Q5-'Wafer Status'!AN5</f>
+        <v>6.6875</v>
+      </c>
+      <c r="N5" s="12">
+        <f>'Wafer Status'!R5-'Wafer Status'!AO5</f>
+        <v>6.45</v>
+      </c>
+      <c r="O5" s="12">
+        <f>'Wafer Status'!S5-'Wafer Status'!AP5</f>
+        <v>6.4849999999999994</v>
+      </c>
+      <c r="P5" s="12">
+        <f>'Wafer Status'!T5-'Wafer Status'!AQ5</f>
+        <v>6.8550000000000004</v>
+      </c>
+      <c r="Q5" s="12">
+        <f>'Wafer Status'!U5-'Wafer Status'!AR5</f>
+        <v>6.1674999999999995</v>
+      </c>
+      <c r="R5" s="12">
+        <f>'Wafer Status'!V5-'Wafer Status'!AS5</f>
+        <v>6.6475</v>
+      </c>
+      <c r="S5" s="12">
+        <f t="shared" si="0"/>
+        <v>6.6990000000000007</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>6.403999999999999</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>6.520999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6">
+        <v>45</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="12">
+        <f>'Wafer Status'!H6-'Wafer Status'!AE6</f>
+        <v>6.51</v>
+      </c>
+      <c r="E6" s="12">
+        <f>'Wafer Status'!I6-'Wafer Status'!AF6</f>
+        <v>1.669999999999999</v>
+      </c>
+      <c r="F6" s="12">
+        <f>'Wafer Status'!J6-'Wafer Status'!AG6</f>
+        <v>1.7674999999999992</v>
+      </c>
+      <c r="G6" s="12">
+        <f>'Wafer Status'!K6-'Wafer Status'!AH6</f>
+        <v>6.625</v>
+      </c>
+      <c r="H6" s="12">
+        <f>'Wafer Status'!L6-'Wafer Status'!AI6</f>
+        <v>2.3549999999999995</v>
+      </c>
+      <c r="I6" s="12">
+        <f>'Wafer Status'!M6-'Wafer Status'!AJ6</f>
+        <v>2.1450000000000005</v>
+      </c>
+      <c r="J6" s="12">
+        <f>'Wafer Status'!N6-'Wafer Status'!AK6</f>
+        <v>6.7149999999999999</v>
+      </c>
+      <c r="K6" s="12">
+        <f>'Wafer Status'!O6-'Wafer Status'!AL6</f>
+        <v>1.6999999999999993</v>
+      </c>
+      <c r="L6" s="12">
+        <f>'Wafer Status'!P6-'Wafer Status'!AM6</f>
+        <v>2.5125000000000002</v>
+      </c>
+      <c r="M6" s="12">
+        <f>'Wafer Status'!Q6-'Wafer Status'!AN6</f>
+        <v>6.8424999999999994</v>
+      </c>
+      <c r="N6" s="12">
+        <f>'Wafer Status'!R6-'Wafer Status'!AO6</f>
+        <v>1.8774999999999995</v>
+      </c>
+      <c r="O6" s="12">
+        <f>'Wafer Status'!S6-'Wafer Status'!AP6</f>
+        <v>1.8724999999999996</v>
+      </c>
+      <c r="P6" s="12">
+        <f>'Wafer Status'!T6-'Wafer Status'!AQ6</f>
+        <v>6.7949999999999999</v>
+      </c>
+      <c r="Q6" s="12">
+        <f>'Wafer Status'!U6-'Wafer Status'!AR6</f>
+        <v>1.2175000000000011</v>
+      </c>
+      <c r="R6" s="12">
+        <f>'Wafer Status'!V6-'Wafer Status'!AS6</f>
+        <v>1.1524999999999999</v>
+      </c>
+      <c r="S6" s="12">
+        <f t="shared" si="0"/>
+        <v>6.6975000000000007</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>1.7639999999999998</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="0"/>
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="12">
+        <f>'Wafer Status'!H7-'Wafer Status'!AE7</f>
+        <v>6.3849999999999998</v>
+      </c>
+      <c r="E7" s="12">
+        <f>'Wafer Status'!I7-'Wafer Status'!AF7</f>
+        <v>4.8324999999999996</v>
+      </c>
+      <c r="F7" s="12">
+        <f>'Wafer Status'!J7-'Wafer Status'!AG7</f>
+        <v>5.24</v>
+      </c>
+      <c r="G7" s="12">
+        <f>'Wafer Status'!K7-'Wafer Status'!AH7</f>
+        <v>6.4525000000000006</v>
+      </c>
+      <c r="H7" s="12">
+        <f>'Wafer Status'!L7-'Wafer Status'!AI7</f>
+        <v>3.9275000000000002</v>
+      </c>
+      <c r="I7" s="12">
+        <f>'Wafer Status'!M7-'Wafer Status'!AJ7</f>
+        <v>4.0924999999999994</v>
+      </c>
+      <c r="J7" s="12">
+        <f>'Wafer Status'!N7-'Wafer Status'!AK7</f>
+        <v>6.5975000000000001</v>
+      </c>
+      <c r="K7" s="12">
+        <f>'Wafer Status'!O7-'Wafer Status'!AL7</f>
+        <v>3.7374999999999994</v>
+      </c>
+      <c r="L7" s="12">
+        <f>'Wafer Status'!P7-'Wafer Status'!AM7</f>
+        <v>4.6775000000000002</v>
+      </c>
+      <c r="M7" s="12">
+        <f>'Wafer Status'!Q7-'Wafer Status'!AN7</f>
+        <v>6.4924999999999997</v>
+      </c>
+      <c r="N7" s="12">
+        <f>'Wafer Status'!R7-'Wafer Status'!AO7</f>
+        <v>4.3375000000000004</v>
+      </c>
+      <c r="O7" s="12">
+        <f>'Wafer Status'!S7-'Wafer Status'!AP7</f>
+        <v>4.5850000000000009</v>
+      </c>
+      <c r="P7" s="12">
+        <f>'Wafer Status'!T7-'Wafer Status'!AQ7</f>
+        <v>6.5550000000000006</v>
+      </c>
+      <c r="Q7" s="12">
+        <f>'Wafer Status'!U7-'Wafer Status'!AR7</f>
+        <v>4.3674999999999997</v>
+      </c>
+      <c r="R7" s="12">
+        <f>'Wafer Status'!V7-'Wafer Status'!AS7</f>
+        <v>4.2925000000000004</v>
+      </c>
+      <c r="S7" s="12">
+        <f t="shared" si="0"/>
+        <v>6.4965000000000002</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>4.2404999999999999</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="0"/>
+        <v>4.5774999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8">
+        <v>37.5</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="12">
+        <f>'Wafer Status'!H8-'Wafer Status'!AE8</f>
+        <v>6.6524999999999999</v>
+      </c>
+      <c r="E8" s="12">
+        <f>'Wafer Status'!I8-'Wafer Status'!AF8</f>
+        <v>2.8774999999999999</v>
+      </c>
+      <c r="F8" s="12">
+        <f>'Wafer Status'!J8-'Wafer Status'!AG8</f>
+        <v>3.3524999999999996</v>
+      </c>
+      <c r="G8" s="12">
+        <f>'Wafer Status'!K8-'Wafer Status'!AH8</f>
+        <v>6.3675000000000006</v>
+      </c>
+      <c r="H8" s="12">
+        <f>'Wafer Status'!L8-'Wafer Status'!AI8</f>
+        <v>3.1574999999999998</v>
+      </c>
+      <c r="I8" s="12">
+        <f>'Wafer Status'!M8-'Wafer Status'!AJ8</f>
+        <v>3.1025000000000005</v>
+      </c>
+      <c r="J8" s="12">
+        <f>'Wafer Status'!N8-'Wafer Status'!AK8</f>
+        <v>6.41</v>
+      </c>
+      <c r="K8" s="12">
+        <f>'Wafer Status'!O8-'Wafer Status'!AL8</f>
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="L8" s="12">
+        <f>'Wafer Status'!P8-'Wafer Status'!AM8</f>
+        <v>2.7300000000000004</v>
+      </c>
+      <c r="M8" s="12">
+        <f>'Wafer Status'!Q8-'Wafer Status'!AN8</f>
+        <v>6.7349999999999994</v>
+      </c>
+      <c r="N8" s="12">
+        <f>'Wafer Status'!R8-'Wafer Status'!AO8</f>
+        <v>3.26</v>
+      </c>
+      <c r="O8" s="12">
+        <f>'Wafer Status'!S8-'Wafer Status'!AP8</f>
+        <v>3.3075000000000001</v>
+      </c>
+      <c r="P8" s="12">
+        <f>'Wafer Status'!T8-'Wafer Status'!AQ8</f>
+        <v>6.6374999999999993</v>
+      </c>
+      <c r="Q8" s="12">
+        <f>'Wafer Status'!U8-'Wafer Status'!AR8</f>
+        <v>3.1850000000000005</v>
+      </c>
+      <c r="R8" s="12">
+        <f>'Wafer Status'!V8-'Wafer Status'!AS8</f>
+        <v>3.2475000000000001</v>
+      </c>
+      <c r="S8" s="12">
+        <f t="shared" si="0"/>
+        <v>6.5604999999999993</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>3.1160000000000001</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>3.1480000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9">
+        <v>25</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="12">
+        <f>'Wafer Status'!H9-'Wafer Status'!AE9</f>
+        <v>6.5124999999999993</v>
+      </c>
+      <c r="E9" s="12">
+        <f>'Wafer Status'!I9-'Wafer Status'!AF9</f>
+        <v>4.32</v>
+      </c>
+      <c r="F9" s="12">
+        <f>'Wafer Status'!J9-'Wafer Status'!AG9</f>
+        <v>4.6775000000000011</v>
+      </c>
+      <c r="G9" s="12">
+        <f>'Wafer Status'!K9-'Wafer Status'!AH9</f>
+        <v>6.6574999999999998</v>
+      </c>
+      <c r="H9" s="12">
+        <f>'Wafer Status'!L9-'Wafer Status'!AI9</f>
+        <v>4.7374999999999998</v>
+      </c>
+      <c r="I9" s="12">
+        <f>'Wafer Status'!M9-'Wafer Status'!AJ9</f>
+        <v>4.5875000000000004</v>
+      </c>
+      <c r="J9" s="12">
+        <f>'Wafer Status'!N9-'Wafer Status'!AK9</f>
+        <v>6.4950000000000001</v>
+      </c>
+      <c r="K9" s="12">
+        <f>'Wafer Status'!O9-'Wafer Status'!AL9</f>
+        <v>4.7874999999999996</v>
+      </c>
+      <c r="L9" s="12">
+        <f>'Wafer Status'!P9-'Wafer Status'!AM9</f>
+        <v>5.1624999999999996</v>
+      </c>
+      <c r="M9" s="12">
+        <f>'Wafer Status'!Q9-'Wafer Status'!AN9</f>
+        <v>6.5400000000000009</v>
+      </c>
+      <c r="N9" s="12">
+        <f>'Wafer Status'!R9-'Wafer Status'!AO9</f>
+        <v>4.3450000000000006</v>
+      </c>
+      <c r="O9" s="12">
+        <f>'Wafer Status'!S9-'Wafer Status'!AP9</f>
+        <v>4.41</v>
+      </c>
+      <c r="P9" s="12">
+        <f>'Wafer Status'!T9-'Wafer Status'!AQ9</f>
+        <v>6.3550000000000004</v>
+      </c>
+      <c r="Q9" s="12">
+        <f>'Wafer Status'!U9-'Wafer Status'!AR9</f>
+        <v>4.6850000000000005</v>
+      </c>
+      <c r="R9" s="12">
+        <f>'Wafer Status'!V9-'Wafer Status'!AS9</f>
+        <v>4.5574999999999992</v>
+      </c>
+      <c r="S9" s="12">
+        <f t="shared" si="0"/>
+        <v>6.5120000000000005</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="0"/>
+        <v>4.5750000000000002</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="0"/>
+        <v>4.6789999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10">
+        <v>55</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="12">
+        <f>'Wafer Status'!AE10</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <f>'Wafer Status'!AF10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <f>'Wafer Status'!AG10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <f>'Wafer Status'!AH10</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
+        <f>'Wafer Status'!AI10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <f>'Wafer Status'!AJ10</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="12">
+        <f>'Wafer Status'!AK10</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12">
+        <f>'Wafer Status'!AL10</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="12">
+        <f>'Wafer Status'!AM10</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
+        <f>'Wafer Status'!AN10</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="12">
+        <f>'Wafer Status'!AO10</f>
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="O10" s="12">
+        <f>'Wafer Status'!AP10</f>
+        <v>0.96249999999999991</v>
+      </c>
+      <c r="P10" s="12">
+        <f>'Wafer Status'!AQ10</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="12">
+        <f>'Wafer Status'!AR10</f>
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="R10" s="12">
+        <f>'Wafer Status'!AS10</f>
+        <v>1.0275000000000001</v>
+      </c>
+      <c r="S10" s="12">
+        <f>'Wafer Status'!AT10</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="12">
+        <f>'Wafer Status'!AU10</f>
+        <v>0.89</v>
+      </c>
+      <c r="U10" s="12">
+        <f>'Wafer Status'!AV10</f>
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="S1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e118d3c-cf2c-4128-9e60-0888f7450af2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007A195C43FE38834190AD02952D649FD7" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0380519f9b74b5abaf62ed559df5e66f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e118d3c-cf2c-4128-9e60-0888f7450af2" xmlns:ns3="dd525dda-2a34-4ca5-a8c9-9cc0327ce268" xmlns:ns4="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8ff845e621325300d74f5263f97ddb6c" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="7e118d3c-cf2c-4128-9e60-0888f7450af2"/>
@@ -3447,17 +4453,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e118d3c-cf2c-4128-9e60-0888f7450af2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3468,6 +4463,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF2F5213-712B-482F-82FD-ACB349A3B196}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd525dda-2a34-4ca5-a8c9-9cc0327ce268"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7e118d3c-cf2c-4128-9e60-0888f7450af2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91C5935B-6E0B-42B8-9F55-FA694CBE5D51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3487,24 +4500,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF2F5213-712B-482F-82FD-ACB349A3B196}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="dd525dda-2a34-4ca5-a8c9-9cc0327ce268"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="7e118d3c-cf2c-4128-9e60-0888f7450af2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F85AB24-DEE0-4E3A-8CB3-12E3FF1F26A5}">
   <ds:schemaRefs>

--- a/EVAP4 Angled Deposition.xlsx
+++ b/EVAP4 Angled Deposition.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mickd\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DB1C4B2-9FFA-40BE-A7FA-F46DF4B0E904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B323C11-0AEC-4E4E-B30D-62FA9E5B05B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" firstSheet="2" activeTab="3" xr2:uid="{D6AA45CB-83A4-4966-9D86-A35E599A57DD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" activeTab="4" xr2:uid="{D6AA45CB-83A4-4966-9D86-A35E599A57DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Process Flow" sheetId="3" r:id="rId1"/>
     <sheet name="Run Sheet" sheetId="5" r:id="rId2"/>
     <sheet name="Wafer Status" sheetId="6" r:id="rId3"/>
     <sheet name="Pad widths" sheetId="7" r:id="rId4"/>
+    <sheet name="Pad widths (2)" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="99">
   <si>
     <t>Step</t>
   </si>
@@ -342,7 +343,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,6 +438,20 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -612,7 +627,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -702,6 +717,18 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -774,8 +801,23 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -792,10 +834,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1575,113 +1613,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:67" ht="14.85" customHeight="1">
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="47" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="48"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="47" t="s">
+      <c r="I1" s="52"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="48"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="47" t="s">
+      <c r="L1" s="52"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="O1" s="48"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="47" t="s">
+      <c r="O1" s="52"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="R1" s="48"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="47" t="s">
+      <c r="R1" s="52"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="U1" s="48"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="41" t="s">
+      <c r="U1" s="52"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="56" t="s">
+      <c r="X1" s="46"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="58"/>
-      <c r="AE1" s="53" t="s">
+      <c r="AA1" s="61"/>
+      <c r="AB1" s="61"/>
+      <c r="AC1" s="61"/>
+      <c r="AD1" s="62"/>
+      <c r="AE1" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="AF1" s="54"/>
-      <c r="AG1" s="55"/>
-      <c r="AH1" s="53" t="s">
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="59"/>
+      <c r="AH1" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="AI1" s="54"/>
-      <c r="AJ1" s="55"/>
-      <c r="AK1" s="53" t="s">
+      <c r="AI1" s="58"/>
+      <c r="AJ1" s="59"/>
+      <c r="AK1" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="AL1" s="54"/>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="53" t="s">
+      <c r="AL1" s="58"/>
+      <c r="AM1" s="59"/>
+      <c r="AN1" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="AO1" s="54"/>
-      <c r="AP1" s="55"/>
-      <c r="AQ1" s="53" t="s">
+      <c r="AO1" s="58"/>
+      <c r="AP1" s="59"/>
+      <c r="AQ1" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="AR1" s="54"/>
-      <c r="AS1" s="55"/>
-      <c r="AT1" s="50" t="s">
+      <c r="AR1" s="58"/>
+      <c r="AS1" s="59"/>
+      <c r="AT1" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="52"/>
+      <c r="AU1" s="55"/>
+      <c r="AV1" s="56"/>
       <c r="AW1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="AX1" s="38" t="s">
+      <c r="AX1" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="AY1" s="39"/>
-      <c r="AZ1" s="40"/>
-      <c r="BA1" s="38" t="s">
+      <c r="AY1" s="43"/>
+      <c r="AZ1" s="44"/>
+      <c r="BA1" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="BB1" s="39"/>
-      <c r="BC1" s="40"/>
-      <c r="BD1" s="38" t="s">
+      <c r="BB1" s="43"/>
+      <c r="BC1" s="44"/>
+      <c r="BD1" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="BE1" s="39"/>
-      <c r="BF1" s="40"/>
-      <c r="BG1" s="38" t="s">
+      <c r="BE1" s="43"/>
+      <c r="BF1" s="44"/>
+      <c r="BG1" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="BH1" s="39"/>
-      <c r="BI1" s="40"/>
-      <c r="BJ1" s="38" t="s">
+      <c r="BH1" s="43"/>
+      <c r="BI1" s="44"/>
+      <c r="BJ1" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="BK1" s="39"/>
-      <c r="BL1" s="40"/>
-      <c r="BM1" s="35" t="s">
+      <c r="BK1" s="43"/>
+      <c r="BL1" s="44"/>
+      <c r="BM1" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="BN1" s="36"/>
-      <c r="BO1" s="37"/>
+      <c r="BN1" s="40"/>
+      <c r="BO1" s="41"/>
     </row>
     <row r="2" spans="1:67" ht="30" customHeight="1">
       <c r="A2" s="25" t="s">
@@ -1910,7 +1948,7 @@
         <v>92</v>
       </c>
       <c r="AE3" s="12">
-        <f t="shared" ref="AE3:AT3" si="1">AVERAGE(0, 0, 0, 0)</f>
+        <f t="shared" ref="AE3:AS3" si="1">AVERAGE(0, 0, 0, 0)</f>
         <v>0</v>
       </c>
       <c r="AF3" s="12">
@@ -1970,11 +2008,11 @@
         <v>0</v>
       </c>
       <c r="AT3" s="12">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(0, 0, 0, 0)</f>
         <v>0</v>
       </c>
       <c r="AU3">
-        <f t="shared" ref="AT3:AV10" si="2">AVERAGE(AF3,AI3,AL3,AO3,AR3)</f>
+        <f t="shared" ref="AU3:AV10" si="2">AVERAGE(AF3,AI3,AL3,AO3,AR3)</f>
         <v>0</v>
       </c>
       <c r="AV3">
@@ -2302,7 +2340,7 @@
         <v>89</v>
       </c>
       <c r="AE5" s="12">
-        <f t="shared" ref="AE5:AT5" si="3">AVERAGE(0, 0, 0, 0)</f>
+        <f t="shared" ref="AE5:AS5" si="3">AVERAGE(0, 0, 0, 0)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="12">
@@ -2362,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="AT5" s="12">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(0, 0, 0, 0)</f>
         <v>0</v>
       </c>
       <c r="AU5">
@@ -3312,25 +3350,43 @@
         <v>55</v>
       </c>
       <c r="AE10" s="9">
-        <f>AF13</f>
-        <v>0</v>
-      </c>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
+        <f>AVERAGE(5.74,5.99,5.62,5.83)</f>
+        <v>5.7949999999999999</v>
+      </c>
+      <c r="AF10" s="12">
+        <f>AVERAGE(0.67,0.79,0.92,0.96)</f>
+        <v>0.83499999999999996</v>
+      </c>
+      <c r="AG10" s="12">
+        <f>AVERAGE(0.74,0.74,0.79,0.76)</f>
+        <v>0.75750000000000006</v>
+      </c>
       <c r="AH10" s="9">
-        <f>AI13</f>
-        <v>0</v>
-      </c>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="12"/>
+        <f>AVERAGE(5.83,5.7,5.87,5.99)</f>
+        <v>5.8475000000000001</v>
+      </c>
+      <c r="AI10" s="12">
+        <f>AVERAGE(0.92,0.83,1.08,0.92)</f>
+        <v>0.9375</v>
+      </c>
+      <c r="AJ10" s="12">
+        <f>AVERAGE(0.74,0.88,1.06,1.02)</f>
+        <v>0.92500000000000004</v>
+      </c>
       <c r="AK10" s="9">
-        <f>AL13</f>
-        <v>0</v>
-      </c>
-      <c r="AL10" s="12"/>
-      <c r="AM10" s="12"/>
+        <f>AJ14</f>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="12">
+        <f>AVERAGE(0.79,1,1.08,1.12)</f>
+        <v>0.99750000000000005</v>
+      </c>
+      <c r="AM10" s="12">
+        <f>AVERAGE(0.91,0.82,0.93,0.86)</f>
+        <v>0.88</v>
+      </c>
       <c r="AN10" s="9">
-        <f>AO13</f>
+        <f>AM14</f>
         <v>0</v>
       </c>
       <c r="AO10" s="12">
@@ -3342,7 +3398,7 @@
         <v>0.96249999999999991</v>
       </c>
       <c r="AQ10" s="9">
-        <f>AR13</f>
+        <f>AP14</f>
         <v>0</v>
       </c>
       <c r="AR10" s="12">
@@ -3359,11 +3415,11 @@
       </c>
       <c r="AU10">
         <f t="shared" si="2"/>
-        <v>0.89</v>
+        <v>0.90999999999999992</v>
       </c>
       <c r="AV10">
         <f t="shared" si="2"/>
-        <v>0.995</v>
+        <v>0.91050000000000009</v>
       </c>
       <c r="AW10" s="10">
         <v>55</v>
@@ -3371,9 +3427,21 @@
     </row>
     <row r="11" spans="1:67" ht="14.4">
       <c r="A11" s="26"/>
+      <c r="AE11" s="12">
+        <f>H10-AE10</f>
+        <v>0.66250000000000053</v>
+      </c>
+      <c r="AH11" s="12">
+        <f>K10-AH10</f>
+        <v>0.82499999999999929</v>
+      </c>
     </row>
     <row r="12" spans="1:67" ht="18.75" customHeight="1">
       <c r="A12" s="26"/>
+      <c r="AF12">
+        <f>AVERAGE(AE11, AH11)</f>
+        <v>0.74374999999999991</v>
+      </c>
     </row>
     <row r="13" spans="1:67" ht="14.4">
       <c r="A13" s="26"/>
@@ -3431,100 +3499,100 @@
     <col min="1" max="21" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="D1" s="53" t="s">
+    <row r="1" spans="1:21" ht="14.4" customHeight="1">
+      <c r="D1" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="54"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="53" t="s">
+      <c r="E1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="H1" s="54"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="53" t="s">
+      <c r="H1" s="64"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="53" t="s">
+      <c r="K1" s="64"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="N1" s="54"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="53" t="s">
+      <c r="N1" s="64"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="50" t="s">
+      <c r="Q1" s="64"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-    </row>
-    <row r="2" spans="1:21" ht="27">
+      <c r="T1" s="67"/>
+      <c r="U1" s="68"/>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="P2" s="33" t="s">
+      <c r="P2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="23" t="s">
+      <c r="R2" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="23" t="s">
+      <c r="U2" s="36" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3575,7 +3643,7 @@
         <v>6.33</v>
       </c>
       <c r="S3" s="12">
-        <f t="shared" ref="S3:U10" si="0">AVERAGE(D3,G3,J3,M3,P3)</f>
+        <f t="shared" ref="S3:U9" si="0">AVERAGE(D3,G3,J3,M3,P3)</f>
         <v>6.5562500000000004</v>
       </c>
       <c r="T3">
@@ -4089,27 +4157,27 @@
       <c r="C10" s="9"/>
       <c r="D10" s="12">
         <f>'Wafer Status'!AE10</f>
-        <v>0</v>
+        <v>5.7949999999999999</v>
       </c>
       <c r="E10" s="12">
         <f>'Wafer Status'!AF10</f>
-        <v>0</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="F10" s="12">
         <f>'Wafer Status'!AG10</f>
-        <v>0</v>
+        <v>0.75750000000000006</v>
       </c>
       <c r="G10" s="12">
         <f>'Wafer Status'!AH10</f>
-        <v>0</v>
+        <v>5.8475000000000001</v>
       </c>
       <c r="H10" s="12">
         <f>'Wafer Status'!AI10</f>
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="I10" s="12">
         <f>'Wafer Status'!AJ10</f>
-        <v>0</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="J10" s="12">
         <f>'Wafer Status'!AK10</f>
@@ -4117,11 +4185,11 @@
       </c>
       <c r="K10" s="12">
         <f>'Wafer Status'!AL10</f>
-        <v>0</v>
+        <v>0.99750000000000005</v>
       </c>
       <c r="L10" s="12">
         <f>'Wafer Status'!AM10</f>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="M10" s="12">
         <f>'Wafer Status'!AN10</f>
@@ -4153,15 +4221,768 @@
       </c>
       <c r="T10" s="12">
         <f>'Wafer Status'!AU10</f>
-        <v>0.89</v>
+        <v>0.90999999999999992</v>
       </c>
       <c r="U10" s="12">
         <f>'Wafer Status'!AV10</f>
-        <v>0.995</v>
+        <v>0.91050000000000009</v>
       </c>
     </row>
     <row r="18" spans="5:5">
-      <c r="E18" s="59"/>
+      <c r="E18" s="38"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23ED2E24-E40F-4A01-AD66-AB8BA9207B1F}">
+  <dimension ref="A1:U18"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="21" width="11.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="14.4" customHeight="1">
+      <c r="D1" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="64"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="63" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" s="64"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="N1" s="64"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="T1" s="67"/>
+      <c r="U1" s="68"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q2" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" s="36" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="12">
+        <f>'Wafer Status'!H3-'Wafer Status'!AE3-'Wafer Status'!$AF$12</f>
+        <v>5.6862499999999994</v>
+      </c>
+      <c r="E3" s="12">
+        <f>'Wafer Status'!I3-'Wafer Status'!AF3-'Wafer Status'!$AF$12</f>
+        <v>6.0787500000000012</v>
+      </c>
+      <c r="F3" s="12">
+        <f>'Wafer Status'!J3-'Wafer Status'!AG3-'Wafer Status'!$AF$12</f>
+        <v>5.6812500000000004</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12">
+        <f>'Wafer Status'!L3-'Wafer Status'!AI3-'Wafer Status'!$AF$12</f>
+        <v>5.6187500000000004</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12">
+        <f>'Wafer Status'!T3-'Wafer Status'!AQ3-'Wafer Status'!$AF$12</f>
+        <v>5.9387500000000006</v>
+      </c>
+      <c r="Q3" s="12">
+        <f>'Wafer Status'!U3-'Wafer Status'!AR3-'Wafer Status'!$AF$12</f>
+        <v>6.1662499999999998</v>
+      </c>
+      <c r="R3" s="12">
+        <f>'Wafer Status'!V3-'Wafer Status'!AS3-'Wafer Status'!$AF$12</f>
+        <v>5.5862499999999997</v>
+      </c>
+      <c r="S3" s="12">
+        <f>'Wafer Status'!W3-'Wafer Status'!AT3-'Wafer Status'!$AF$12</f>
+        <v>5.8125</v>
+      </c>
+      <c r="T3" s="12">
+        <f>'Wafer Status'!X3-'Wafer Status'!AU3-'Wafer Status'!$AF$12</f>
+        <v>5.9545833333333338</v>
+      </c>
+      <c r="U3" s="12">
+        <f>'Wafer Status'!Y3-'Wafer Status'!AV3-'Wafer Status'!$AF$12</f>
+        <v>5.6337500000000009</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="12">
+        <f>'Wafer Status'!H4-'Wafer Status'!AE4-'Wafer Status'!$AF$12</f>
+        <v>6.2612499999999986</v>
+      </c>
+      <c r="E4" s="12">
+        <f>'Wafer Status'!I4-'Wafer Status'!AF4-'Wafer Status'!$AF$12</f>
+        <v>4.1987499999999986</v>
+      </c>
+      <c r="F4" s="12">
+        <f>'Wafer Status'!J4-'Wafer Status'!AG4-'Wafer Status'!$AF$12</f>
+        <v>4.3462499999999995</v>
+      </c>
+      <c r="G4" s="12">
+        <f>'Wafer Status'!K4-'Wafer Status'!AH4-'Wafer Status'!$AF$12</f>
+        <v>5.6487499999999997</v>
+      </c>
+      <c r="H4" s="12">
+        <f>'Wafer Status'!L4-'Wafer Status'!AI4-'Wafer Status'!$AF$12</f>
+        <v>4.1112500000000001</v>
+      </c>
+      <c r="I4" s="12">
+        <f>'Wafer Status'!M4-'Wafer Status'!AJ4-'Wafer Status'!$AF$12</f>
+        <v>4.1937499999999996</v>
+      </c>
+      <c r="J4" s="12">
+        <f>'Wafer Status'!N4-'Wafer Status'!AK4-'Wafer Status'!$AF$12</f>
+        <v>5.9862500000000001</v>
+      </c>
+      <c r="K4" s="12">
+        <f>'Wafer Status'!O4-'Wafer Status'!AL4-'Wafer Status'!$AF$12</f>
+        <v>4.5662500000000001</v>
+      </c>
+      <c r="L4" s="12">
+        <f>'Wafer Status'!P4-'Wafer Status'!AM4-'Wafer Status'!$AF$12</f>
+        <v>3.9762500000000007</v>
+      </c>
+      <c r="M4" s="12">
+        <f>'Wafer Status'!Q4-'Wafer Status'!AN4-'Wafer Status'!$AF$12</f>
+        <v>6.0112499999999986</v>
+      </c>
+      <c r="N4" s="12">
+        <f>'Wafer Status'!R4-'Wafer Status'!AO4-'Wafer Status'!$AF$12</f>
+        <v>3.9137500000000007</v>
+      </c>
+      <c r="O4" s="12">
+        <f>'Wafer Status'!S4-'Wafer Status'!AP4-'Wafer Status'!$AF$12</f>
+        <v>4.0912500000000005</v>
+      </c>
+      <c r="P4" s="12">
+        <f>'Wafer Status'!T4-'Wafer Status'!AQ4-'Wafer Status'!$AF$12</f>
+        <v>5.7987500000000001</v>
+      </c>
+      <c r="Q4" s="12">
+        <f>'Wafer Status'!U4-'Wafer Status'!AR4-'Wafer Status'!$AF$12</f>
+        <v>4.1387499999999999</v>
+      </c>
+      <c r="R4" s="12">
+        <f>'Wafer Status'!V4-'Wafer Status'!AS4-'Wafer Status'!$AF$12</f>
+        <v>4.15625</v>
+      </c>
+      <c r="S4" s="12">
+        <f>'Wafer Status'!W4-'Wafer Status'!AT4-'Wafer Status'!$AF$12</f>
+        <v>5.9412500000000001</v>
+      </c>
+      <c r="T4" s="12">
+        <f>'Wafer Status'!X4-'Wafer Status'!AU4-'Wafer Status'!$AF$12</f>
+        <v>4.1857500000000005</v>
+      </c>
+      <c r="U4" s="12">
+        <f>'Wafer Status'!Y4-'Wafer Status'!AV4-'Wafer Status'!$AF$12</f>
+        <v>4.1527500000000011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="12">
+        <f>'Wafer Status'!H5-'Wafer Status'!AE5-'Wafer Status'!$AF$12</f>
+        <v>6.0112500000000004</v>
+      </c>
+      <c r="E5" s="12">
+        <f>'Wafer Status'!I5-'Wafer Status'!AF5-'Wafer Status'!$AF$12</f>
+        <v>5.8912499999999994</v>
+      </c>
+      <c r="F5" s="12">
+        <f>'Wafer Status'!J5-'Wafer Status'!AG5-'Wafer Status'!$AF$12</f>
+        <v>6.0262499999999992</v>
+      </c>
+      <c r="G5" s="12">
+        <f>'Wafer Status'!K5-'Wafer Status'!AH5-'Wafer Status'!$AF$12</f>
+        <v>5.8837499999999991</v>
+      </c>
+      <c r="H5" s="12">
+        <f>'Wafer Status'!L5-'Wafer Status'!AI5-'Wafer Status'!$AF$12</f>
+        <v>5.5437500000000011</v>
+      </c>
+      <c r="I5" s="12">
+        <f>'Wafer Status'!M5-'Wafer Status'!AJ5-'Wafer Status'!$AF$12</f>
+        <v>5.6037499999999998</v>
+      </c>
+      <c r="J5" s="12">
+        <f>'Wafer Status'!N5-'Wafer Status'!AK5-'Wafer Status'!$AF$12</f>
+        <v>5.8262499999999999</v>
+      </c>
+      <c r="K5" s="12">
+        <f>'Wafer Status'!O5-'Wafer Status'!AL5-'Wafer Status'!$AF$12</f>
+        <v>5.7362500000000001</v>
+      </c>
+      <c r="L5" s="12">
+        <f>'Wafer Status'!P5-'Wafer Status'!AM5-'Wafer Status'!$AF$12</f>
+        <v>5.6112500000000001</v>
+      </c>
+      <c r="M5" s="12">
+        <f>'Wafer Status'!Q5-'Wafer Status'!AN5-'Wafer Status'!$AF$12</f>
+        <v>5.9437499999999996</v>
+      </c>
+      <c r="N5" s="12">
+        <f>'Wafer Status'!R5-'Wafer Status'!AO5-'Wafer Status'!$AF$12</f>
+        <v>5.7062500000000007</v>
+      </c>
+      <c r="O5" s="12">
+        <f>'Wafer Status'!S5-'Wafer Status'!AP5-'Wafer Status'!$AF$12</f>
+        <v>5.7412499999999991</v>
+      </c>
+      <c r="P5" s="12">
+        <f>'Wafer Status'!T5-'Wafer Status'!AQ5-'Wafer Status'!$AF$12</f>
+        <v>6.1112500000000001</v>
+      </c>
+      <c r="Q5" s="12">
+        <f>'Wafer Status'!U5-'Wafer Status'!AR5-'Wafer Status'!$AF$12</f>
+        <v>5.4237500000000001</v>
+      </c>
+      <c r="R5" s="12">
+        <f>'Wafer Status'!V5-'Wafer Status'!AS5-'Wafer Status'!$AF$12</f>
+        <v>5.9037500000000005</v>
+      </c>
+      <c r="S5" s="12">
+        <f>'Wafer Status'!W5-'Wafer Status'!AT5-'Wafer Status'!$AF$12</f>
+        <v>5.9552500000000013</v>
+      </c>
+      <c r="T5" s="12">
+        <f>'Wafer Status'!X5-'Wafer Status'!AU5-'Wafer Status'!$AF$12</f>
+        <v>5.6602499999999996</v>
+      </c>
+      <c r="U5" s="12">
+        <f>'Wafer Status'!Y5-'Wafer Status'!AV5-'Wafer Status'!$AF$12</f>
+        <v>5.7772499999999987</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6">
+        <v>45</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="12">
+        <f>'Wafer Status'!H6-'Wafer Status'!AE6-'Wafer Status'!$AF$12</f>
+        <v>5.7662499999999994</v>
+      </c>
+      <c r="E6" s="12">
+        <f>'Wafer Status'!I6-'Wafer Status'!AF6-'Wafer Status'!$AF$12</f>
+        <v>0.92624999999999913</v>
+      </c>
+      <c r="F6" s="12">
+        <f>'Wafer Status'!J6-'Wafer Status'!AG6-'Wafer Status'!$AF$12</f>
+        <v>1.0237499999999993</v>
+      </c>
+      <c r="G6" s="12">
+        <f>'Wafer Status'!K6-'Wafer Status'!AH6-'Wafer Status'!$AF$12</f>
+        <v>5.8812499999999996</v>
+      </c>
+      <c r="H6" s="12">
+        <f>'Wafer Status'!L6-'Wafer Status'!AI6-'Wafer Status'!$AF$12</f>
+        <v>1.6112499999999996</v>
+      </c>
+      <c r="I6" s="12">
+        <f>'Wafer Status'!M6-'Wafer Status'!AJ6-'Wafer Status'!$AF$12</f>
+        <v>1.4012500000000006</v>
+      </c>
+      <c r="J6" s="12">
+        <f>'Wafer Status'!N6-'Wafer Status'!AK6-'Wafer Status'!$AF$12</f>
+        <v>5.9712499999999995</v>
+      </c>
+      <c r="K6" s="12">
+        <f>'Wafer Status'!O6-'Wafer Status'!AL6-'Wafer Status'!$AF$12</f>
+        <v>0.95624999999999938</v>
+      </c>
+      <c r="L6" s="12">
+        <f>'Wafer Status'!P6-'Wafer Status'!AM6-'Wafer Status'!$AF$12</f>
+        <v>1.7687500000000003</v>
+      </c>
+      <c r="M6" s="12">
+        <f>'Wafer Status'!Q6-'Wafer Status'!AN6-'Wafer Status'!$AF$12</f>
+        <v>6.098749999999999</v>
+      </c>
+      <c r="N6" s="12">
+        <f>'Wafer Status'!R6-'Wafer Status'!AO6-'Wafer Status'!$AF$12</f>
+        <v>1.1337499999999996</v>
+      </c>
+      <c r="O6" s="12">
+        <f>'Wafer Status'!S6-'Wafer Status'!AP6-'Wafer Status'!$AF$12</f>
+        <v>1.1287499999999997</v>
+      </c>
+      <c r="P6" s="12">
+        <f>'Wafer Status'!T6-'Wafer Status'!AQ6-'Wafer Status'!$AF$12</f>
+        <v>6.0512499999999996</v>
+      </c>
+      <c r="Q6" s="12">
+        <f>'Wafer Status'!U6-'Wafer Status'!AR6-'Wafer Status'!$AF$12</f>
+        <v>0.47375000000000123</v>
+      </c>
+      <c r="R6" s="12">
+        <f>'Wafer Status'!V6-'Wafer Status'!AS6-'Wafer Status'!$AF$12</f>
+        <v>0.40874999999999995</v>
+      </c>
+      <c r="S6" s="12">
+        <f>'Wafer Status'!W6-'Wafer Status'!AT6-'Wafer Status'!$AF$12</f>
+        <v>5.9537500000000012</v>
+      </c>
+      <c r="T6" s="12">
+        <f>'Wafer Status'!X6-'Wafer Status'!AU6-'Wafer Status'!$AF$12</f>
+        <v>1.0202500000000003</v>
+      </c>
+      <c r="U6" s="12">
+        <f>'Wafer Status'!Y6-'Wafer Status'!AV6-'Wafer Status'!$AF$12</f>
+        <v>1.1462500000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="12">
+        <f>'Wafer Status'!H7-'Wafer Status'!AE7-'Wafer Status'!$AF$12</f>
+        <v>5.6412499999999994</v>
+      </c>
+      <c r="E7" s="12">
+        <f>'Wafer Status'!I7-'Wafer Status'!AF7-'Wafer Status'!$AF$12</f>
+        <v>4.0887499999999992</v>
+      </c>
+      <c r="F7" s="12">
+        <f>'Wafer Status'!J7-'Wafer Status'!AG7-'Wafer Status'!$AF$12</f>
+        <v>4.4962499999999999</v>
+      </c>
+      <c r="G7" s="12">
+        <f>'Wafer Status'!K7-'Wafer Status'!AH7-'Wafer Status'!$AF$12</f>
+        <v>5.7087500000000002</v>
+      </c>
+      <c r="H7" s="12">
+        <f>'Wafer Status'!L7-'Wafer Status'!AI7-'Wafer Status'!$AF$12</f>
+        <v>3.1837500000000003</v>
+      </c>
+      <c r="I7" s="12">
+        <f>'Wafer Status'!M7-'Wafer Status'!AJ7-'Wafer Status'!$AF$12</f>
+        <v>3.3487499999999994</v>
+      </c>
+      <c r="J7" s="12">
+        <f>'Wafer Status'!N7-'Wafer Status'!AK7-'Wafer Status'!$AF$12</f>
+        <v>5.8537499999999998</v>
+      </c>
+      <c r="K7" s="12">
+        <f>'Wafer Status'!O7-'Wafer Status'!AL7-'Wafer Status'!$AF$12</f>
+        <v>2.9937499999999995</v>
+      </c>
+      <c r="L7" s="12">
+        <f>'Wafer Status'!P7-'Wafer Status'!AM7-'Wafer Status'!$AF$12</f>
+        <v>3.9337500000000003</v>
+      </c>
+      <c r="M7" s="12">
+        <f>'Wafer Status'!Q7-'Wafer Status'!AN7-'Wafer Status'!$AF$12</f>
+        <v>5.7487499999999994</v>
+      </c>
+      <c r="N7" s="12">
+        <f>'Wafer Status'!R7-'Wafer Status'!AO7-'Wafer Status'!$AF$12</f>
+        <v>3.5937500000000004</v>
+      </c>
+      <c r="O7" s="12">
+        <f>'Wafer Status'!S7-'Wafer Status'!AP7-'Wafer Status'!$AF$12</f>
+        <v>3.8412500000000009</v>
+      </c>
+      <c r="P7" s="12">
+        <f>'Wafer Status'!T7-'Wafer Status'!AQ7-'Wafer Status'!$AF$12</f>
+        <v>5.8112500000000011</v>
+      </c>
+      <c r="Q7" s="12">
+        <f>'Wafer Status'!U7-'Wafer Status'!AR7-'Wafer Status'!$AF$12</f>
+        <v>3.6237499999999998</v>
+      </c>
+      <c r="R7" s="12">
+        <f>'Wafer Status'!V7-'Wafer Status'!AS7-'Wafer Status'!$AF$12</f>
+        <v>3.5487500000000005</v>
+      </c>
+      <c r="S7" s="12">
+        <f>'Wafer Status'!W7-'Wafer Status'!AT7-'Wafer Status'!$AF$12</f>
+        <v>5.7527500000000007</v>
+      </c>
+      <c r="T7" s="12">
+        <f>'Wafer Status'!X7-'Wafer Status'!AU7-'Wafer Status'!$AF$12</f>
+        <v>3.4967499999999991</v>
+      </c>
+      <c r="U7" s="12">
+        <f>'Wafer Status'!Y7-'Wafer Status'!AV7-'Wafer Status'!$AF$12</f>
+        <v>3.8337500000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8">
+        <v>37.5</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="12">
+        <f>'Wafer Status'!H8-'Wafer Status'!AE8-'Wafer Status'!$AF$12</f>
+        <v>5.9087499999999995</v>
+      </c>
+      <c r="E8" s="12">
+        <f>'Wafer Status'!I8-'Wafer Status'!AF8-'Wafer Status'!$AF$12</f>
+        <v>2.13375</v>
+      </c>
+      <c r="F8" s="12">
+        <f>'Wafer Status'!J8-'Wafer Status'!AG8-'Wafer Status'!$AF$12</f>
+        <v>2.6087499999999997</v>
+      </c>
+      <c r="G8" s="12">
+        <f>'Wafer Status'!K8-'Wafer Status'!AH8-'Wafer Status'!$AF$12</f>
+        <v>5.6237500000000011</v>
+      </c>
+      <c r="H8" s="12">
+        <f>'Wafer Status'!L8-'Wafer Status'!AI8-'Wafer Status'!$AF$12</f>
+        <v>2.4137499999999998</v>
+      </c>
+      <c r="I8" s="12">
+        <f>'Wafer Status'!M8-'Wafer Status'!AJ8-'Wafer Status'!$AF$12</f>
+        <v>2.3587500000000006</v>
+      </c>
+      <c r="J8" s="12">
+        <f>'Wafer Status'!N8-'Wafer Status'!AK8-'Wafer Status'!$AF$12</f>
+        <v>5.6662499999999998</v>
+      </c>
+      <c r="K8" s="12">
+        <f>'Wafer Status'!O8-'Wafer Status'!AL8-'Wafer Status'!$AF$12</f>
+        <v>2.3562499999999997</v>
+      </c>
+      <c r="L8" s="12">
+        <f>'Wafer Status'!P8-'Wafer Status'!AM8-'Wafer Status'!$AF$12</f>
+        <v>1.9862500000000005</v>
+      </c>
+      <c r="M8" s="12">
+        <f>'Wafer Status'!Q8-'Wafer Status'!AN8-'Wafer Status'!$AF$12</f>
+        <v>5.9912499999999991</v>
+      </c>
+      <c r="N8" s="12">
+        <f>'Wafer Status'!R8-'Wafer Status'!AO8-'Wafer Status'!$AF$12</f>
+        <v>2.5162499999999999</v>
+      </c>
+      <c r="O8" s="12">
+        <f>'Wafer Status'!S8-'Wafer Status'!AP8-'Wafer Status'!$AF$12</f>
+        <v>2.5637500000000002</v>
+      </c>
+      <c r="P8" s="12">
+        <f>'Wafer Status'!T8-'Wafer Status'!AQ8-'Wafer Status'!$AF$12</f>
+        <v>5.8937499999999989</v>
+      </c>
+      <c r="Q8" s="12">
+        <f>'Wafer Status'!U8-'Wafer Status'!AR8-'Wafer Status'!$AF$12</f>
+        <v>2.4412500000000006</v>
+      </c>
+      <c r="R8" s="12">
+        <f>'Wafer Status'!V8-'Wafer Status'!AS8-'Wafer Status'!$AF$12</f>
+        <v>2.5037500000000001</v>
+      </c>
+      <c r="S8" s="12">
+        <f>'Wafer Status'!W8-'Wafer Status'!AT8-'Wafer Status'!$AF$12</f>
+        <v>5.816749999999999</v>
+      </c>
+      <c r="T8" s="12">
+        <f>'Wafer Status'!X8-'Wafer Status'!AU8-'Wafer Status'!$AF$12</f>
+        <v>2.3722499999999989</v>
+      </c>
+      <c r="U8" s="12">
+        <f>'Wafer Status'!Y8-'Wafer Status'!AV8-'Wafer Status'!$AF$12</f>
+        <v>2.4042499999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9">
+        <v>25</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="12">
+        <f>'Wafer Status'!H9-'Wafer Status'!AE9-'Wafer Status'!$AF$12</f>
+        <v>5.7687499999999989</v>
+      </c>
+      <c r="E9" s="12">
+        <f>'Wafer Status'!I9-'Wafer Status'!AF9-'Wafer Status'!$AF$12</f>
+        <v>3.5762500000000004</v>
+      </c>
+      <c r="F9" s="12">
+        <f>'Wafer Status'!J9-'Wafer Status'!AG9-'Wafer Status'!$AF$12</f>
+        <v>3.9337500000000012</v>
+      </c>
+      <c r="G9" s="12">
+        <f>'Wafer Status'!K9-'Wafer Status'!AH9-'Wafer Status'!$AF$12</f>
+        <v>5.9137500000000003</v>
+      </c>
+      <c r="H9" s="12">
+        <f>'Wafer Status'!L9-'Wafer Status'!AI9-'Wafer Status'!$AF$12</f>
+        <v>3.9937499999999999</v>
+      </c>
+      <c r="I9" s="12">
+        <f>'Wafer Status'!M9-'Wafer Status'!AJ9-'Wafer Status'!$AF$12</f>
+        <v>3.8437500000000004</v>
+      </c>
+      <c r="J9" s="12">
+        <f>'Wafer Status'!N9-'Wafer Status'!AK9-'Wafer Status'!$AF$12</f>
+        <v>5.7512500000000006</v>
+      </c>
+      <c r="K9" s="12">
+        <f>'Wafer Status'!O9-'Wafer Status'!AL9-'Wafer Status'!$AF$12</f>
+        <v>4.0437499999999993</v>
+      </c>
+      <c r="L9" s="12">
+        <f>'Wafer Status'!P9-'Wafer Status'!AM9-'Wafer Status'!$AF$12</f>
+        <v>4.4187499999999993</v>
+      </c>
+      <c r="M9" s="12">
+        <f>'Wafer Status'!Q9-'Wafer Status'!AN9-'Wafer Status'!$AF$12</f>
+        <v>5.7962500000000006</v>
+      </c>
+      <c r="N9" s="12">
+        <f>'Wafer Status'!R9-'Wafer Status'!AO9-'Wafer Status'!$AF$12</f>
+        <v>3.6012500000000007</v>
+      </c>
+      <c r="O9" s="12">
+        <f>'Wafer Status'!S9-'Wafer Status'!AP9-'Wafer Status'!$AF$12</f>
+        <v>3.6662500000000002</v>
+      </c>
+      <c r="P9" s="12">
+        <f>'Wafer Status'!T9-'Wafer Status'!AQ9-'Wafer Status'!$AF$12</f>
+        <v>5.6112500000000001</v>
+      </c>
+      <c r="Q9" s="12">
+        <f>'Wafer Status'!U9-'Wafer Status'!AR9-'Wafer Status'!$AF$12</f>
+        <v>3.9412500000000006</v>
+      </c>
+      <c r="R9" s="12">
+        <f>'Wafer Status'!V9-'Wafer Status'!AS9-'Wafer Status'!$AF$12</f>
+        <v>3.8137499999999993</v>
+      </c>
+      <c r="S9" s="12">
+        <f>'Wafer Status'!W9-'Wafer Status'!AT9-'Wafer Status'!$AF$12</f>
+        <v>5.7682500000000001</v>
+      </c>
+      <c r="T9" s="12">
+        <f>'Wafer Status'!X9-'Wafer Status'!AU9-'Wafer Status'!$AF$12</f>
+        <v>3.8312499999999994</v>
+      </c>
+      <c r="U9" s="12">
+        <f>'Wafer Status'!Y9-'Wafer Status'!AV9-'Wafer Status'!$AF$12</f>
+        <v>3.9352499999999986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10">
+        <v>55</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="12">
+        <f>'Wafer Status'!AE10</f>
+        <v>5.7949999999999999</v>
+      </c>
+      <c r="E10" s="12">
+        <f>'Wafer Status'!AF10</f>
+        <v>0.83499999999999996</v>
+      </c>
+      <c r="F10" s="12">
+        <f>'Wafer Status'!AG10</f>
+        <v>0.75750000000000006</v>
+      </c>
+      <c r="G10" s="12">
+        <f>'Wafer Status'!AH10</f>
+        <v>5.8475000000000001</v>
+      </c>
+      <c r="H10" s="12">
+        <f>'Wafer Status'!AI10</f>
+        <v>0.9375</v>
+      </c>
+      <c r="I10" s="12">
+        <f>'Wafer Status'!AJ10</f>
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="J10" s="12">
+        <f>'Wafer Status'!N10-'Wafer Status'!AK10-'Wafer Status'!$AF$12</f>
+        <v>5.6612500000000008</v>
+      </c>
+      <c r="K10" s="12">
+        <f>'Wafer Status'!AL10</f>
+        <v>0.99750000000000005</v>
+      </c>
+      <c r="L10" s="12">
+        <f>'Wafer Status'!AM10</f>
+        <v>0.88</v>
+      </c>
+      <c r="M10" s="12">
+        <f>'Wafer Status'!Q10-'Wafer Status'!AN10-'Wafer Status'!$AF$12</f>
+        <v>5.8837499999999991</v>
+      </c>
+      <c r="N10" s="12">
+        <f>'Wafer Status'!AO10</f>
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="O10" s="12">
+        <f>'Wafer Status'!AP10</f>
+        <v>0.96249999999999991</v>
+      </c>
+      <c r="P10" s="12">
+        <f>'Wafer Status'!T10-'Wafer Status'!AQ10-'Wafer Status'!$AF$12</f>
+        <v>5.8787500000000001</v>
+      </c>
+      <c r="Q10" s="12">
+        <f>'Wafer Status'!AR10</f>
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="R10" s="12">
+        <f>'Wafer Status'!AS10</f>
+        <v>1.0275000000000001</v>
+      </c>
+      <c r="S10" s="12">
+        <f>'Wafer Status'!W10-'Wafer Status'!AT10-'Wafer Status'!$AF$12</f>
+        <v>5.81325</v>
+      </c>
+      <c r="T10" s="12">
+        <f>'Wafer Status'!AU10</f>
+        <v>0.90999999999999992</v>
+      </c>
+      <c r="U10" s="12">
+        <f>'Wafer Status'!AV10</f>
+        <v>0.91050000000000009</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4465,17 +5286,17 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF2F5213-712B-482F-82FD-ACB349A3B196}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="dd525dda-2a34-4ca5-a8c9-9cc0327ce268"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd525dda-2a34-4ca5-a8c9-9cc0327ce268"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="7e118d3c-cf2c-4128-9e60-0888f7450af2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
